--- a/docs/DermaClub_Aliases_DRAFT_2026-08-28.xlsx
+++ b/docs/DermaClub_Aliases_DRAFT_2026-08-28.xlsx
@@ -997,17 +997,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>سكين بوستر|سكين بوسترز|بوسترات البشرة</t>
+          <t>سكين بوستر|سكين بوسترز|بوسترات البشرة|حقن ترطيب ونضارة البشرة|معززات البشرة</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>drafted</t>
+          <t>client-approved</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>حقن نضارة is the term most patients use, but it also covers mesotherapy, which is not in this catalogue. Left off pending the clinic's answer — see open question 3.</t>
+          <t>Q3, answered by the clinic. The transliterations are kept beside their words: both are what patients type.</t>
         </is>
       </c>
     </row>
@@ -1329,15 +1329,19 @@
           <t>Annual Half Body (12 Sessions)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ليزر سنوي 12 جلسة هاف بودي|ليزر نص الجسم 12 جلسة سنوي</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>client-approved</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Indistinguishable from DT023 in Arabic — both are a 12-session annual half-body laser package (17,800 vs 14,300). No alias until the clinic says what a patient asks for differently. See open question 1.</t>
+          <t>Q1, answered. The clinic gave ليزر 12 جلسة نص الجسم to this package and to DT023; one string cannot name two rows, so it sits here in the clinic's own longer form and on DT023 in theirs. A patient using the shorter phrase reaches both and is asked which.</t>
         </is>
       </c>
     </row>
@@ -1398,15 +1402,19 @@
           <t>Laser Hair Removal Half Body Annual 12 Sessions</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ليزر سنوي هاف بودي 12 جلسة|باقة هاف بودي نص سنوي|باقة ليزر نصف الجسم هاف بودي|ليزر نص الجسم 12 جلسة</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>client-approved</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>See DT020 and open question 1.</t>
+          <t>Q1, answered. See DT020 for the one phrase the clinic gave to both.</t>
         </is>
       </c>
     </row>
@@ -1421,15 +1429,19 @@
           <t>Laser Hair Removal Maintenance 4 Sessions</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>باقة متابعة الليزر 4 جلسات|باقة 4 جلسات متابعة ازالة شعر</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>client-approved</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Indistinguishable from DT027 in Arabic — both are a 4-session maintenance package (6,900 vs 8,600). See open question 2.</t>
+          <t>Q2, answered. Distinguished from DT027 by what the clinic left out of it: no جسم كامل, no فل بودي.</t>
         </is>
       </c>
     </row>
@@ -1494,15 +1506,19 @@
           <t>Maintenance Package (4 Sessions Full Body)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4 جلسات متابعة ليزر جسم كامل|متابعة ليزر 4 جلسات فل بودي|متابعة 4 جلسات فل بودي</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>client-approved</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>See DT024 and open question 2.</t>
+          <t>Q2, answered. Every name the clinic gave this one says full body, which is what separates it from DT024.</t>
         </is>
       </c>
     </row>

--- a/docs/DermaClub_Aliases_DRAFT_2026-08-28.xlsx
+++ b/docs/DermaClub_Aliases_DRAFT_2026-08-28.xlsx
@@ -1329,19 +1329,15 @@
           <t>Annual Half Body (12 Sessions)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ليزر سنوي 12 جلسة هاف بودي|ليزر نص الجسم 12 جلسة سنوي</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>client-approved</t>
+          <t>not-wired</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Q1, answered. The clinic gave ليزر 12 جلسة نص الجسم to this package and to DT023; one string cannot name two rows, so it sits here in the clinic's own longer form and on DT023 in theirs. A patient using the shorter phrase reaches both and is asked which.</t>
+          <t>Deliberately left unwired at the clinic's instruction. The row stays in the list so the decision is visible rather than looking like an omission: DT020 answers to its English catalogue name and to nothing in Arabic, and every Arabic half-body phrase now reaches DT023 alone.</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1410,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Q1, answered. See DT020 for the one phrase the clinic gave to both.</t>
+          <t>Q1, answered. The only half-body package with Arabic names: DT020 is deliberately unwired, so every Arabic phrasing lands here.</t>
         </is>
       </c>
     </row>

--- a/docs/DermaClub_Aliases_DRAFT_2026-08-28.xlsx
+++ b/docs/DermaClub_Aliases_DRAFT_2026-08-28.xlsx
@@ -1166,17 +1166,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>بيوستيميوليتور|بيو ستيميوليتور</t>
+          <t>محفزات الكولاجين|محفز الكولاجين|بيوستيميوليتور|بيو ستيميوليتور</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>drafted</t>
+          <t>client-approved</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Transliteration only. Many patients call this محفزات الكولاجين — needs the clinic's word before it goes in (open question 3).</t>
+          <t>Q3, answered by the clinic. Their words first, the transliterations kept behind them: patients type both.</t>
         </is>
       </c>
     </row>
